--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_IDEFICS_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_IDEFICS_FRANZI.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{CCAD57CC-B1E3-42EB-AA6F-5642678A746A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{68140089-BBF9-486E-BCD1-79260BE80421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="340">
   <si>
     <t>index</t>
   </si>
@@ -781,143 +786,99 @@
     <t>integer</t>
   </si>
   <si>
-    <t>D19</t>
-  </si>
-  <si>
     <t>direct_mapping</t>
   </si>
   <si>
-    <t>SACANA FGS D19 "Potatoes and other starchy vegetables"</t>
-  </si>
-  <si>
     <t xml:space="preserve">complete </t>
   </si>
   <si>
     <t>identical</t>
   </si>
   <si>
-    <t>operation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">compatible </t>
-  </si>
-  <si>
     <t xml:space="preserve">impossible </t>
   </si>
   <si>
     <t>unavailable</t>
   </si>
   <si>
-    <t>D18</t>
-  </si>
-  <si>
-    <t>SACANA FGS D18 vegetables n.s.</t>
-  </si>
-  <si>
-    <t>L44c</t>
-  </si>
-  <si>
-    <t>SACANA FGS L44c "Mixed salad"</t>
-  </si>
-  <si>
-    <t>D17;L44;L46a</t>
-  </si>
-  <si>
-    <t>D20</t>
-  </si>
-  <si>
-    <t>SACANA FGS D20 "Fruits n.s."</t>
-  </si>
-  <si>
-    <t>D20a</t>
-  </si>
-  <si>
     <t xml:space="preserve">SACANA FGS D20a "Fresh fruits" </t>
   </si>
   <si>
-    <t>D16a</t>
-  </si>
-  <si>
     <t>SACANA FGS D16a "Nuts and seeds"</t>
   </si>
   <si>
-    <t>D16b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partial </t>
-  </si>
-  <si>
-    <t>tentative</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
     <t>SACANA FGS J37a "Milk plain whole" + SACANA FGS J37b "Milk plain reduced fat"</t>
   </si>
   <si>
-    <t>J37c</t>
-  </si>
-  <si>
     <t xml:space="preserve">SACANA FGS J37c "Chocolate milk, vanilla milk and sim" </t>
   </si>
   <si>
-    <t>J37d;J37e;J37f;J37g</t>
-  </si>
-  <si>
     <t>SACANA FGS J37d "Yogurt, probiotic and other fermented milk unsweened, full fat" + SACANA FGS J37e "Yogurt, probiotic and other fermented milk unsweened, low fat" + SACANA FGS J37f "Sweet Yogurt, probiotic and other fermented milk , full fat" + SACANA FGS J37g "Sweet Yogurt, probiotic and other fermented milk, low fat"</t>
   </si>
   <si>
-    <t>J38</t>
-  </si>
-  <si>
-    <t>SACANA FGS J38 "Cheese n.s."</t>
-  </si>
-  <si>
-    <t>J39a</t>
-  </si>
-  <si>
-    <t>J39c;K40b</t>
-  </si>
-  <si>
     <t>SACANA FGS J39c "cream" + SACANA FGS K40b "Vegetal milk (soymilk, rice milk etc.)"</t>
   </si>
   <si>
-    <t>J39c</t>
-  </si>
-  <si>
     <t>SACANA FGS J39c "cream"</t>
   </si>
   <si>
-    <t>K40b</t>
-  </si>
-  <si>
     <t>SACANA FGS K40b "Vegetal milk (soymilk, rice milk etc.)"</t>
   </si>
   <si>
-    <t>A;L43;L45c</t>
-  </si>
-  <si>
-    <t>A01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACANA FGS A01 "bread,rolls and sim. ns" </t>
-  </si>
-  <si>
-    <t>A01a;A01b</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)" </t>
+    <t>SACANA FGS G32 "Offals"</t>
+  </si>
+  <si>
+    <t>SACANA FGS H35 "Processed fish products"</t>
+  </si>
+  <si>
+    <t>SACANA FGS C13 "margarines and lipids of mixed origin"</t>
+  </si>
+  <si>
+    <t>SACANA FGS B08 "Sugar, honey, jam and sweet sauces or dessert sauces "</t>
+  </si>
+  <si>
+    <t>SACANA FGS 22 "water"</t>
+  </si>
+  <si>
+    <t>impossible</t>
+  </si>
+  <si>
+    <t>SACANA FGS K40a "Vegetarian burgers, tempeh, tofu, seitan"</t>
+  </si>
+  <si>
+    <t>IDEFICS_P1</t>
+  </si>
+  <si>
+    <t>_BLANK_</t>
+  </si>
+  <si>
+    <t>paste</t>
+  </si>
+  <si>
+    <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" + SACANA FGS J38c "Sweetened cheese and curd"</t>
+  </si>
+  <si>
+    <t>SACANA FGS K40c "Soy based dessert, cakes,and similar"</t>
+  </si>
+  <si>
+    <t>2 (24HDR)</t>
+  </si>
+  <si>
+    <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns"</t>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS D19 "Potatoes and other starchy vegetables" + SACANA FGS 19a " Potatoes cooked (not deep fried)" + SACANA FGS 19b " Potatoes cooked (deep fried)" + (</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Gewichtung?</t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gewichtung</t>
     </r>
     <r>
       <rPr>
@@ -926,286 +887,651 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
+      <t>* SACANA FGS L47 "Based on potatoes")</t>
+    </r>
+  </si>
+  <si>
+    <t>SACANA FGS D20 "Fruits n.s." + SACANA FGS D20a "Fresh fruits" + SACANA FGS 16a "Nuts and seeds"</t>
+  </si>
+  <si>
+    <t>SACANA FGS D20 "Fruits n.s." + SACANA FGS D20b</t>
+  </si>
+  <si>
+    <t>SACANA FGS J38 "Cheese n.s." + SACANA FGS J38a "Cheese low fat and curd (unsweetened)" + SACANA FGS J38b "Cheese medium fat/full fat (unsweetened)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS A02a " complete breakfast cereals/flakes unsweetened, (sugar &lt;15%), wholemeal (fiber&gt;5%)" + SACANA FGS A02b "complete breakfast cereals/flakes sweetened (sugar&gt;15%), wholemeal (fiber&gt;5%)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS G29 "meat (other than poultry)-ns" + SACANA FGS G29a "meat - very fatty cut / fatty preparation (fat &gt;10%)" + SACANA FGS G29b "meat -low fat preparation/ lean cut and (fat &lt;10%)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS G30a " poultry fatty preparation (fat&gt;10%)" + SACANA FGS G30b "poultry non fatty preparation (fat&lt;10%)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS G33 " Processed meat,salami, processed poultry products , meat salad- ns" + G33a "Fatty/ very fatty items (fat &gt;20%)" + G33b "Lean/very lean items (fat &lt;20%)" + G33c "liver, blood and derived processed meats"</t>
+  </si>
+  <si>
+    <t>SACANA FGS H34 "Fish and seafood" + SACANA FGS H34a + SACANA FGS H34b</t>
+  </si>
+  <si>
+    <t>SACANA FGS I36 " eggs and simple egg recipes (not fried)" + I37 "eggs and simple egg recipes (fried, stirfried)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS C12 "vegetable oils ns" + C12a "olive oil" + C12b " other vegetable oils" + C13 "margarines and lipids of mixed origin" + C14 "butter and animal fats"</t>
+  </si>
+  <si>
+    <t>SACANA FGS C12 "vegetable oils + C12a "olive oil" + C12b " other vegetable oils"</t>
+  </si>
+  <si>
+    <t>SACANA FGS C14 "butter and animal fats"</t>
+  </si>
+  <si>
+    <t>SACANA FGS B08 "Sugar, honey, jam and sweet sauces or dessert sauces " + B09 "Confectionery (non chocolate)" + B09b "Candies, candy bars, chewing gum, (with sugar)" + B10a "chocolate bars , chocolate coated nuts, confetti, twix, lion, mars" + B10b "chocolate spread, paste, powder, sauce" + B11 " Other sugar product - ns" + B11a "marzipan, sugar coated peanuts/almonds. nutspread" + B11b "water ice, sorbet (excluding ice cream)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS B10a "chocolate bars , chocolate coated nuts, confetti, twix, lion, mars" + B10b "chocolate spread, paste, powder, sauce"</t>
+  </si>
+  <si>
+    <t>SACANA FGS B09 "Confectionery (non chocolate)" + B09b "Candies, candy bars, chewing gum, (with sugar)</t>
+  </si>
+  <si>
+    <t>SACANA FGS A06 "Sweet bakery, biscuits, pies (sweet), cakes , sweet fritters and other confectionery" + A06a "(fat &gt;20%)" + A06b "(fat &lt;20%)"</t>
+  </si>
+  <si>
+    <t>SACANA FGS E24 "fruit, vegetable juices and smoothies - ns" + E24b "fruit (and vegetable) juices - manufactured"</t>
+  </si>
+  <si>
+    <t>SACANA FGS E25a "carbonated drink (sweetened )" + E25b "carbonated drink (low calory, reduced sugar")</t>
+  </si>
+  <si>
+    <t>SACANA FGS E22 "water" + E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" + E24 "fruit, vegetable juices and smoothies - ns" + E24b "fruit (and vegetable) juices - manufactured" + E25 "Soft and sweetened drinks" + E25a "carbonated drink (sweetened )" + E25b "carbonated drink (low calory, reduced sugar)" + E25c "other drinks normally sweetened"</t>
+  </si>
+  <si>
+    <t>SACANA FGS C15 "Sauces, dressing and condiments - ns" + C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" + C15c "Very Low/no calory condiments and other minor ingredients" + C15d "Based on meat" + C15e "Based on vegetables" + C15f "Based on dairy" + C15h "Based on meat, cheese, eggs, vegs"</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SACANA FGS C15 "Sauces, dressing and condiments - ns" + C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" + C15c "Very Low/no calory condiments and other minor ingredients" + C15d "Based on meat" + C15e "Based on vegetables" + C15f "Based on dairy" + C15h "Based on meat, cheese, eggs, vegs" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minus herbs, spices and condiments</t>
+    </r>
+  </si>
+  <si>
+    <t>SACANA FGS L44a "Soup, veloutè, LIQUID"</t>
+  </si>
+  <si>
+    <t>SACANA FGS E21 " Bouillon - meat/fish/vegetable"</t>
+  </si>
+  <si>
+    <t>SACANA FGS K40a "Vegetarian burgers, tempeh, tofu, seitan" + K40c "Soy based dessert, cakes,and similar"</t>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> D18a "Vegetables raw") + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">D18b "Vegetables cooked or preserved (not deep fried)" + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D18c"Vegetable cooked (deep fried) "</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> D18a "Vegetables raw") + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> D18b "Vegetables cooked or preserved (not deep fried)"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> D18a "Vegetables raw") + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D18b "Vegetables cooked or preserved (not deep fried)"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D18a "Vegetables raw") + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> D18b "Vegetables cooked or preserved (not deep fried)"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D18b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D18a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D18b "Vegetables cooked or preserved (not deep fried) + "SACANA FGS L44c "Mixed salad"</t>
+    </r>
+  </si>
+  <si>
+    <t>sum of all items related to vegetables (as indicated in separate Excel sheet)</t>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS D16b "Olives and avocados" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Only proportion of o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lives</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <t>SACANA FGS A01a " bread, crispbread, rusks, roll (refined, fiber &lt;5%)" + SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)" (</t>
+    <t>Sum of all items in SACANA FGS J37 to J39c and K40b</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SACANA FGS J38a "Cheese low fat and curd (unsweetened)" </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung?</t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Only proportion of curd</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <t>A02</t>
-  </si>
-  <si>
-    <t>SACANA FGS A02 "breakfast cereals, corn flakes, muesli ns"</t>
-  </si>
-  <si>
-    <t>G;L42;L45b</t>
-  </si>
-  <si>
-    <t>G29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACANA FGS G29 "meat (other than poultry)-ns" </t>
-  </si>
-  <si>
-    <t>G30</t>
-  </si>
-  <si>
-    <t>SACANA FGS G30 "poultry-ns"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G31 </t>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS G31 "rabbit and game" (</t>
+    <r>
+      <t>all items for SACANA FGS A01a to A06b + SACANA FGS L43 "Based on Cereals ns" + (</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung?</t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SACANA FGS L45c "with vegs/potatoes/cereals")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS A04 "Pasta (any kind)" + SACANA FGS A05 " rice and other cereal grains (not ready to eat) - ns" + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SACANA FGS L43a "Pasta/rice/cereals + meat/fish/eggs/cheese") + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SACANA FGS L43b "Pasta/rice/cereals + legumes /vegetables/potatoes")</t>
+    </r>
+  </si>
+  <si>
+    <t>SACANA FGS A07 only items "Knabbergebäck" und "Kräcker"</t>
+  </si>
+  <si>
+    <r>
+      <t>all items for SACANA FGS G29 to G33c  + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SACANA FGS L42 "based on meat") + (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SACANA FGS L45b "with meat/fish")</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">all items from H34" Fish and seafood" + H34a "Fish, fatty preparation" + H34b "Fish, lean preparation" + H35 "Processed fish products" </t>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>only Milcheis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + B11b "water ice, sorbet (excluding ice cream)"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of Milcheis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <t>G33</t>
-  </si>
-  <si>
-    <t>SACANA FGS G33 " Processed meat,salami, processed poultry products , meat salad- ns"</t>
-  </si>
-  <si>
-    <t>G32</t>
-  </si>
-  <si>
-    <t>SACANA FGS G32 "Offals"</t>
-  </si>
-  <si>
-    <t>H34</t>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS H34 "Fish and seafood" (</t>
+    <r>
+      <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung?</t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of Sorbet</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <t>H35</t>
-  </si>
-  <si>
-    <t>SACANA FGS H35 "Processed fish products"</t>
-  </si>
-  <si>
-    <t>C12;C13;C14</t>
-  </si>
-  <si>
-    <t>SACANA FGS C12 "vegetable oils ns" + SACANA FGS C13 "margarines and lipids of mixed origin" + SACANA FGS C14 "butter and animal fats"</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>SACANA FGS C12 "vegetable oils ns"</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>SACANA FGS C13 "margarines and lipids of mixed origin"</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>SACANA FGS B "Sugar and sugar products"</t>
-  </si>
-  <si>
-    <t>B08</t>
-  </si>
-  <si>
-    <t>SACANA FGS B08 "Sugar, honey, jam and sweet sauces or dessert sauces "</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>SACANA FGS B10 "Chocolate ns"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B09 </t>
-  </si>
-  <si>
-    <t>SACANA FGS B09 "Confectionery (non chocolate)"</t>
-  </si>
-  <si>
-    <t>B11b</t>
-  </si>
-  <si>
-    <t>A06</t>
-  </si>
-  <si>
-    <t>SACANA FGS A06 " Sweet bakery, biscuits, pies (sweet), cakes , sweet fritters and other confectionery"</t>
-  </si>
-  <si>
-    <t>E22;E23;E24;E25</t>
-  </si>
-  <si>
-    <t>E24</t>
-  </si>
-  <si>
-    <t>E25</t>
-  </si>
-  <si>
-    <t>E23</t>
-  </si>
-  <si>
-    <t>E22</t>
-  </si>
-  <si>
-    <t>SACANA FGS 22 "water"</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACANA FGS F "Alcoholic beverages ns" </t>
-  </si>
-  <si>
-    <t>F27</t>
-  </si>
-  <si>
-    <t>SACANA FGS F27 "Wine"</t>
-  </si>
-  <si>
-    <t>F26</t>
-  </si>
-  <si>
-    <t>SACANA FGS F26 "Beer and cider"</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACANA FGS C15 Sauces, dressing and condiments - ns </t>
-  </si>
-  <si>
-    <t>E21;L44a;L44b</t>
-  </si>
-  <si>
-    <t>SACANA FGS E21 " Bouillon - meat/fish/vegetable" + SACANA FGS L44a "Soup, veloutè, LIQUID" + SACANA FGS L44b "Soup, veloutè, NOT LIQUID"</t>
-  </si>
-  <si>
-    <t>impossible</t>
-  </si>
-  <si>
-    <t>K40a</t>
-  </si>
-  <si>
-    <t>SACANA FGS K40a "Vegetarian burgers, tempeh, tofu, seitan"</t>
-  </si>
-  <si>
-    <t>A04;A05;L43a;L43b</t>
-  </si>
-  <si>
-    <t>J37a;J37b</t>
-  </si>
-  <si>
-    <t>H;L45b;L46</t>
-  </si>
-  <si>
-    <t>I;L45</t>
-  </si>
-  <si>
-    <t>IDEFICS_P1</t>
-  </si>
-  <si>
-    <t>_BLANK_</t>
-  </si>
-  <si>
-    <t>paste</t>
-  </si>
-  <si>
-    <t>D19a; D19b;L47</t>
-  </si>
-  <si>
-    <r>
-      <t>D19a + D19b + (</t>
+    <r>
+      <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting</t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of Wassereis</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*L47)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>D17 + (</t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS C15e (</t>
     </r>
     <r>
       <rPr>
@@ -1215,7 +1541,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t>Proportion Tomatensoße</t>
     </r>
     <r>
       <rPr>
@@ -1225,7 +1551,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> *L44) + (</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" + C15f "Based on dairy" (</t>
     </r>
     <r>
       <rPr>
@@ -1235,7 +1566,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t>Proportion  Dressings?</t>
     </r>
     <r>
       <rPr>
@@ -1245,10 +1576,13 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*L46a)</t>
-    </r>
-  </si>
-  <si>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS C15a "Cold sauces &gt;40% fat" (</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1257,7 +1591,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Weighting</t>
+      <t>Proportion</t>
     </r>
     <r>
       <rPr>
@@ -1267,33 +1601,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*D16b</t>
-    </r>
-  </si>
-  <si>
-    <t>J37a + J37b</t>
-  </si>
-  <si>
-    <t>J37d+J37e+J37f+J37g</t>
-  </si>
-  <si>
-    <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" + SACANA FGS J38c "Sweetened cheese and curd"</t>
-  </si>
-  <si>
-    <t>J38a</t>
-  </si>
-  <si>
-    <t>J39a;J38c</t>
-  </si>
-  <si>
-    <t>J39a + J38c</t>
-  </si>
-  <si>
-    <t>J39c + K40b</t>
-  </si>
-  <si>
-    <r>
-      <t>A + L43 + (</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1303,7 +1611,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t xml:space="preserve"> Mayonnaise?</t>
     </r>
     <r>
       <rPr>
@@ -1313,12 +1621,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*L45c)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>A04 + A05 +(</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS C15c "Very Low/no calory condiments and other minor ingredients" (</t>
     </r>
     <r>
       <rPr>
@@ -1328,7 +1636,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t>Proportion Fruchtsoße?</t>
     </r>
     <r>
       <rPr>
@@ -1338,7 +1646,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*L43a) + (</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS C15c "Very Low/no calory condiments and other minor ingredients" (</t>
     </r>
     <r>
       <rPr>
@@ -1348,7 +1661,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t>Proportion Herbs, Spices?</t>
     </r>
     <r>
       <rPr>
@@ -1358,27 +1671,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*L43b)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS D16b "Olives and avocados" (</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS C15a "Cold sauces &gt;40% fat" + C15b "Cold sauces &lt;40% fat" (</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung für Oliven?</t>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion Condiments?</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <charset val="1"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
@@ -1386,6 +1701,9 @@
   </si>
   <si>
     <r>
+      <t>SACANA FGS E21 " Bouillon - meat/fish/vegetable" + SACANA FGS L44a "Soup, veloutè, LIQUID" + SACANA FGS L44b "Soup, veloutè, NOT LIQUID" (</t>
+    </r>
+    <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
@@ -1393,7 +1711,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t>Proportion Suppen, Eintöpfe?</t>
     </r>
     <r>
       <rPr>
@@ -1403,12 +1721,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*J38a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS J38a "Cheese low fat and curd (unsweetened)" (</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns"</t>
     </r>
     <r>
       <rPr>
@@ -1418,7 +1742,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Gewichtung für Curd?</t>
+      <t xml:space="preserve"> (Proportion Malzkaffee?)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion Tee (Früchte und Kräuter)?</t>
     </r>
     <r>
       <rPr>
@@ -1433,7 +1772,7 @@
   </si>
   <si>
     <r>
-      <t>G + L42 + (</t>
+      <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns"  (</t>
     </r>
     <r>
       <rPr>
@@ -1443,7 +1782,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting</t>
+      <t>Proportion Tee (grün und schwarz)?)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion Kaffee</t>
     </r>
     <r>
       <rPr>
@@ -1453,12 +1807,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>* L45b)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS G "Meat and meat products" + SACANA FGS L42 "based on meat" + (</t>
+      <t>?)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS D17 Pulses n.s. + (</t>
     </r>
     <r>
       <rPr>
@@ -1468,20 +1822,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Gewichtung*</t>
+      <t xml:space="preserve">Proportion of </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> SACANA FGS L45b "with meat/fish")</t>
-    </r>
-  </si>
-  <si>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L44 "Legumes/Vegs n.s.")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SACANA FGS D19 "Potatoes and other starchy vegetables" + SACANA FGS 19a " Potatoes cooked (not deep fried)" + SACANA FGS 19b " Potatoes cooked (deep fried)" + (</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1490,590 +1846,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>weighting*</t>
+      <t>Proportion of</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G31</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>G32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>H + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L45b) + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*L46)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS H"Finfish, shelfish and their products" + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SACANA FGS L45b "with meat/fish") + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*SACANA FGS L46 "Based on fish")</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>H34</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I+ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*L45)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS I "Eggs" + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L45 "based on eggs")</t>
-    </r>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>SACANA FGS I "Eggs"</t>
-  </si>
-  <si>
-    <t>C12 + C13 + C14</t>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS C14 "butter and animal fats" (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung für Butter?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS C14 "butter and animal fats" (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung für animal fat?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*J39a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung für Sorbet?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)" (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung für Wassereis?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weighting*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>B11b</t>
-    </r>
-  </si>
-  <si>
-    <t>E22 + E23 + E24 + E25</t>
-  </si>
-  <si>
-    <t>E21 + L44a + L44b</t>
-  </si>
-  <si>
-    <t>SACANA FGS K40c "Soy based dessert, cakes,and similar"</t>
-  </si>
-  <si>
-    <t>K40c</t>
-  </si>
-  <si>
-    <t>2 (24HDR)</t>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS D19a " Potatoes cooked (not deep fried) " + SACANA FGS 19b " Potatoes cooked (deep fried) " + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> SACANA FGS L47 "Based on potatoes")</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS D17 Pulses n.s. + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*L44 "Legumes/Vegs n.s.") + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L46a "Fish and vegetables/legumes")</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SACANA FGS J "Dairy and similar" </t>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS A " Cereals and cereal products and starchy snacks ns" + SACANA FGS L43 "Based on Cereals ns" + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*SACANA FGS L45c "with vegs/potatoes/cereals")</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">(A01a + A01b) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>* weighting</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding" (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung für Milcheis?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SACANA FGS A04 "Pasta (any kind)" + SACANA FGS A05 " rice and other cereal grains (not ready to eat) - ns" + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SACANA FGS L43a "Pasta/rice/cereals + meat/fish/eggs/cheese") + (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gewichtung</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*SACANA FGS L43b "Pasta/rice/cereals + legumes /vegetables/potatoes")</t>
-    </r>
-  </si>
-  <si>
-    <t>SACANA FGS E22 "water" + SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns" + SACANA FGS E24 "fruit, vegetable juices and smoothies - ns" + SACANA FGS E25 "Soft and sweetened drinks"</t>
-  </si>
-  <si>
-    <t>SACANA FGS E24 "fruit, vegetable juices and smoothies - ns"</t>
-  </si>
-  <si>
-    <t>SACANA FGS E25 "Soft and sweetened drinks"</t>
-  </si>
-  <si>
-    <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns"</t>
   </si>
 </sst>
 </file>
@@ -2136,18 +1919,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2162,7 +1939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2178,25 +1955,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2205,7 +1963,20 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2214,6 +1985,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFF2CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2226,9 +2002,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2266,9 +2042,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2301,26 +2077,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2353,26 +2112,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2549,17 +2291,20 @@
   <dimension ref="A1:AC121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="34.5703125" customWidth="1"/>
-    <col min="9" max="9" width="167.42578125" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" customWidth="1"/>
+    <col min="8" max="8" width="40.85546875" customWidth="1"/>
+    <col min="9" max="9" width="113.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="93.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2594,7 +2339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -2605,28 +2350,30 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -2637,28 +2384,30 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="L3" s="10"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -2669,26 +2418,27 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>18</v>
       </c>
@@ -2699,28 +2449,29 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>355</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>263</v>
+        <v>253</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -2731,26 +2482,28 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>355</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>22</v>
       </c>
@@ -2761,26 +2514,28 @@
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>24</v>
       </c>
@@ -2791,26 +2546,28 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>355</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>26</v>
       </c>
@@ -2821,26 +2578,28 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>355</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>28</v>
       </c>
@@ -2851,26 +2610,28 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>30</v>
       </c>
@@ -2881,26 +2642,28 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>355</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>32</v>
       </c>
@@ -2911,26 +2674,28 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>355</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>34</v>
       </c>
@@ -2941,26 +2706,28 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>355</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>36</v>
       </c>
@@ -2971,28 +2738,28 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>355</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>264</v>
+        <v>273</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>38</v>
       </c>
@@ -3003,28 +2770,28 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>355</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>40</v>
       </c>
@@ -3035,23 +2802,23 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="2:29" x14ac:dyDescent="0.25">
@@ -3065,26 +2832,27 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>355</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="M17" s="3"/>
     </row>
     <row r="18" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
@@ -3097,25 +2865,25 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>355</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="2:29" x14ac:dyDescent="0.25">
@@ -3129,25 +2897,25 @@
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>355</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
+      </c>
+      <c r="F19" t="s">
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.25">
@@ -3161,24 +2929,27 @@
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>355</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I20" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="J20" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>261</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="M20" s="3"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
@@ -3191,26 +2962,27 @@
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>355</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>275</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M21" s="3"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
@@ -3223,26 +2995,27 @@
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>355</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>257</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M22" s="3"/>
     </row>
     <row r="23" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
@@ -3255,25 +3028,25 @@
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>355</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>362</v>
+        <v>273</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" t="s">
+        <v>253</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.25">
@@ -3287,25 +3060,25 @@
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>355</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>254</v>
+        <v>273</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H24" t="s">
+        <v>253</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.25">
@@ -3319,25 +3092,25 @@
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>355</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>363</v>
+        <v>273</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" t="s">
+        <v>253</v>
+      </c>
+      <c r="H25" t="s">
+        <v>253</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.25">
@@ -3351,26 +3124,27 @@
         <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>355</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>275</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="F26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" t="s">
+        <v>253</v>
+      </c>
+      <c r="H26" t="s">
+        <v>253</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M26" s="3"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
@@ -3383,25 +3157,25 @@
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>355</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I27" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" t="s">
+        <v>253</v>
+      </c>
+      <c r="H27" t="s">
+        <v>253</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>257</v>
+      <c r="J27" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.25">
@@ -3415,25 +3189,25 @@
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>355</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>367</v>
+        <v>273</v>
+      </c>
+      <c r="F28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" t="s">
+        <v>253</v>
+      </c>
+      <c r="H28" t="s">
+        <v>253</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>259</v>
+        <v>276</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="2:29" x14ac:dyDescent="0.25">
@@ -3447,44 +3221,44 @@
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>355</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="17"/>
+        <v>273</v>
+      </c>
+      <c r="F29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" t="s">
+        <v>253</v>
+      </c>
+      <c r="H29" t="s">
+        <v>253</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+      <c r="AA29" s="10"/>
+      <c r="AB29" s="10"/>
+      <c r="AC29" s="10"/>
     </row>
     <row r="30" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
@@ -3497,25 +3271,25 @@
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>355</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>254</v>
+        <v>273</v>
+      </c>
+      <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" t="s">
+        <v>253</v>
+      </c>
+      <c r="H30" t="s">
+        <v>253</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.25">
@@ -3529,25 +3303,25 @@
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>355</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>254</v>
+        <v>273</v>
+      </c>
+      <c r="F31" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" t="s">
+        <v>253</v>
+      </c>
+      <c r="H31" t="s">
+        <v>253</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.25">
@@ -3561,26 +3335,26 @@
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>74</v>
       </c>
@@ -3591,28 +3365,29 @@
         <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>355</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>258</v>
+        <v>273</v>
+      </c>
+      <c r="F33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s">
+        <v>253</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>369</v>
+        <v>253</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>401</v>
+        <v>318</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>76</v>
       </c>
@@ -3623,26 +3398,26 @@
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>78</v>
       </c>
@@ -3653,28 +3428,29 @@
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>355</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F35" t="s">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s">
+        <v>253</v>
+      </c>
+      <c r="H35" t="s">
+        <v>253</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M35" s="10"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>80</v>
       </c>
@@ -3685,28 +3461,29 @@
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>355</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F36" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s">
+        <v>253</v>
+      </c>
+      <c r="H36" t="s">
+        <v>253</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M36" s="7"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>82</v>
       </c>
@@ -3717,28 +3494,29 @@
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>355</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" t="s">
+        <v>253</v>
+      </c>
+      <c r="H37" t="s">
+        <v>253</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>84</v>
       </c>
@@ -3749,28 +3527,29 @@
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>355</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" t="s">
+        <v>253</v>
+      </c>
+      <c r="H38" t="s">
+        <v>253</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>86</v>
       </c>
@@ -3781,28 +3560,29 @@
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>355</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F39" t="s">
+        <v>86</v>
+      </c>
+      <c r="G39" t="s">
+        <v>253</v>
+      </c>
+      <c r="H39" t="s">
+        <v>253</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>88</v>
       </c>
@@ -3813,26 +3593,29 @@
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>355</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I40" s="5"/>
-      <c r="J40" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F40" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" t="s">
+        <v>253</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>90</v>
       </c>
@@ -3843,26 +3626,26 @@
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I41" s="16"/>
-      <c r="J41" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>92</v>
       </c>
@@ -3873,28 +3656,29 @@
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>355</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F42" t="s">
+        <v>92</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>94</v>
       </c>
@@ -3905,28 +3689,29 @@
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>355</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>301</v>
+        <v>273</v>
+      </c>
+      <c r="F43" t="s">
+        <v>94</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>96</v>
       </c>
@@ -3937,26 +3722,29 @@
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>355</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I44" s="16"/>
-      <c r="J44" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F44" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>98</v>
       </c>
@@ -3967,26 +3755,29 @@
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>355</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I45" s="16"/>
-      <c r="J45" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>100</v>
       </c>
@@ -3997,26 +3788,29 @@
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>355</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I46" s="16"/>
-      <c r="J46" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F46" t="s">
+        <v>100</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>102</v>
       </c>
@@ -4027,26 +3821,29 @@
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>355</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I47" s="16"/>
-      <c r="J47" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F47" t="s">
+        <v>102</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>104</v>
       </c>
@@ -4057,26 +3854,27 @@
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I48" s="16"/>
-      <c r="J48" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>106</v>
       </c>
@@ -4087,26 +3885,26 @@
         <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I49" s="16"/>
-      <c r="J49" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>108</v>
       </c>
@@ -4117,28 +3915,29 @@
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>355</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>302</v>
+        <v>273</v>
+      </c>
+      <c r="F50" t="s">
+        <v>108</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>303</v>
+        <v>253</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>110</v>
       </c>
@@ -4149,26 +3948,26 @@
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I51" s="16"/>
-      <c r="J51" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K51" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="I51" s="9"/>
+      <c r="J51" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>112</v>
       </c>
@@ -4179,26 +3978,29 @@
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>355</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F52" t="s">
+        <v>112</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I52" s="16"/>
-      <c r="J52" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>114</v>
       </c>
@@ -4209,26 +4011,29 @@
         <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>355</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F53" t="s">
+        <v>114</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I53" s="16"/>
-      <c r="J53" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>116</v>
       </c>
@@ -4239,26 +4044,29 @@
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>355</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F54" t="s">
+        <v>116</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I54" s="16"/>
-      <c r="J54" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K54" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>118</v>
       </c>
@@ -4269,26 +4077,27 @@
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I55" s="16"/>
-      <c r="J55" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="K55" s="14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>120</v>
       </c>
@@ -4299,28 +4108,27 @@
         <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>355</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="J56" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>122</v>
       </c>
@@ -4331,28 +4139,27 @@
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>355</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K57" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>124</v>
       </c>
@@ -4363,28 +4170,29 @@
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>355</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>306</v>
+        <v>273</v>
+      </c>
+      <c r="F58" t="s">
+        <v>124</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>307</v>
+        <v>253</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>126</v>
       </c>
@@ -4395,28 +4203,28 @@
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>355</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>308</v>
+        <v>273</v>
+      </c>
+      <c r="F59" t="s">
+        <v>126</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>128</v>
       </c>
@@ -4427,29 +4235,30 @@
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>355</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
+        <v>273</v>
+      </c>
+      <c r="F60" t="s">
+        <v>128</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="10" t="s">
         <v>130</v>
       </c>
       <c r="C61" t="s">
@@ -4459,29 +4268,30 @@
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>355</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="J61" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K61" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
+        <v>273</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" s="10" t="s">
         <v>132</v>
       </c>
       <c r="C62" t="s">
@@ -4491,28 +4301,29 @@
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>355</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="I62" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="J62" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K62" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K62" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>134</v>
       </c>
@@ -4523,28 +4334,28 @@
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>355</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>312</v>
+        <v>273</v>
+      </c>
+      <c r="F63" t="s">
+        <v>134</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H63" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>136</v>
       </c>
@@ -4555,28 +4366,29 @@
         <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>355</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="K64" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F64" t="s">
+        <v>136</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>138</v>
       </c>
@@ -4587,28 +4399,27 @@
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>383</v>
+        <v>271</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>384</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I65" s="5"/>
       <c r="J65" s="3" t="s">
         <v>256</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>140</v>
       </c>
@@ -4619,28 +4430,28 @@
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>355</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F66" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>142</v>
       </c>
@@ -4651,28 +4462,28 @@
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>355</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>317</v>
+        <v>273</v>
+      </c>
+      <c r="F67" t="s">
+        <v>142</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>144</v>
       </c>
@@ -4683,28 +4494,29 @@
         <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>355</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>387</v>
+        <v>273</v>
+      </c>
+      <c r="F68" t="s">
+        <v>144</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>253</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="J68" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K68" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K68" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M68" s="12"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>146</v>
       </c>
@@ -4715,28 +4527,28 @@
         <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>355</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>319</v>
+        <v>273</v>
+      </c>
+      <c r="F69" t="s">
+        <v>146</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>320</v>
+        <v>268</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>148</v>
       </c>
@@ -4747,26 +4559,26 @@
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>150</v>
       </c>
@@ -4777,26 +4589,26 @@
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H71" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>152</v>
       </c>
@@ -4807,28 +4619,27 @@
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>355</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="J72" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K72" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="K72" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="M72" s="12"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>154</v>
       </c>
@@ -4839,28 +4650,28 @@
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>355</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>321</v>
+        <v>273</v>
+      </c>
+      <c r="F73" t="s">
+        <v>154</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>322</v>
+        <v>253</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>156</v>
       </c>
@@ -4871,28 +4682,28 @@
         <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>355</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>323</v>
+        <v>273</v>
+      </c>
+      <c r="F74" t="s">
+        <v>156</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>324</v>
+        <v>269</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>158</v>
       </c>
@@ -4903,28 +4714,28 @@
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>355</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>325</v>
+        <v>273</v>
+      </c>
+      <c r="F75" t="s">
+        <v>158</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H75" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>326</v>
+        <v>253</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>160</v>
       </c>
@@ -4935,28 +4746,28 @@
         <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>355</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>327</v>
+        <v>273</v>
+      </c>
+      <c r="F76" t="s">
+        <v>160</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>328</v>
+        <v>253</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>162</v>
       </c>
@@ -4967,27 +4778,27 @@
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H77" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B78" s="10" t="s">
         <v>164</v>
       </c>
       <c r="C78" t="s">
@@ -4997,26 +4808,29 @@
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>355</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H78" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I78" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J78" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M78" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>166</v>
       </c>
@@ -5027,28 +4841,29 @@
         <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>355</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="K79" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F79" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="K79" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M79" s="3"/>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>168</v>
       </c>
@@ -5059,28 +4874,29 @@
         <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>355</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="I80" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="K80" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F80" t="s">
+        <v>168</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I80" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>170</v>
       </c>
@@ -5091,28 +4907,29 @@
         <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>355</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="K81" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F81" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I81" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>172</v>
       </c>
@@ -5123,28 +4940,28 @@
         <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>355</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>330</v>
+        <v>273</v>
+      </c>
+      <c r="F82" t="s">
+        <v>172</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H82" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>331</v>
+        <v>253</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>174</v>
       </c>
@@ -5155,26 +4972,26 @@
         <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H83" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I83" s="5"/>
       <c r="J83" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>176</v>
       </c>
@@ -5185,26 +5002,26 @@
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H84" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I84" s="5"/>
       <c r="J84" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>178</v>
       </c>
@@ -5215,28 +5032,28 @@
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>355</v>
-      </c>
-      <c r="F85" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="G85" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H85" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="I85" s="16" t="s">
-        <v>405</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="K85" s="14" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="F85" t="s">
+        <v>178</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>180</v>
       </c>
@@ -5247,28 +5064,28 @@
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>355</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>333</v>
+        <v>273</v>
+      </c>
+      <c r="F86" t="s">
+        <v>180</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H86" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>406</v>
+        <v>253</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>182</v>
       </c>
@@ -5279,28 +5096,28 @@
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>355</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>334</v>
+        <v>273</v>
+      </c>
+      <c r="F87" t="s">
+        <v>182</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H87" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I87" s="5" t="s">
-        <v>407</v>
+        <v>253</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>184</v>
       </c>
@@ -5311,148 +5128,160 @@
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>355</v>
-      </c>
-      <c r="F88" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F88" t="s">
+        <v>184</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="10"/>
+      <c r="B89" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="10"/>
+      <c r="B90" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="10"/>
+      <c r="B91" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I91" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H88" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>186</v>
-      </c>
-      <c r="C89" t="s">
-        <v>187</v>
-      </c>
-      <c r="D89" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" t="s">
-        <v>355</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H89" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I89" s="5"/>
-      <c r="J89" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>188</v>
-      </c>
-      <c r="C90" t="s">
-        <v>189</v>
-      </c>
-      <c r="D90" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" t="s">
-        <v>355</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H90" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I90" s="5"/>
-      <c r="J90" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>190</v>
-      </c>
-      <c r="C91" t="s">
-        <v>191</v>
-      </c>
-      <c r="D91" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" t="s">
-        <v>355</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H91" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I91" s="5"/>
       <c r="J91" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="10"/>
+      <c r="B92" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D92" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" t="s">
-        <v>355</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>348</v>
+      <c r="D92" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H92" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I92" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I92" s="14" t="s">
+        <v>334</v>
+      </c>
       <c r="J92" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>194</v>
       </c>
@@ -5463,28 +5292,28 @@
         <v>13</v>
       </c>
       <c r="E93" t="s">
-        <v>355</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>336</v>
+        <v>273</v>
+      </c>
+      <c r="F93" t="s">
+        <v>194</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H93" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>337</v>
+        <v>270</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>196</v>
       </c>
@@ -5495,20 +5324,18 @@
         <v>13</v>
       </c>
       <c r="E94" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H94" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>339</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I94" s="2"/>
       <c r="J94" s="3" t="s">
         <v>256</v>
       </c>
@@ -5516,7 +5343,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>198</v>
       </c>
@@ -5527,20 +5354,18 @@
         <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>340</v>
+        <v>271</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H95" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>341</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I95" s="2"/>
       <c r="J95" s="3" t="s">
         <v>256</v>
       </c>
@@ -5548,7 +5373,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>200</v>
       </c>
@@ -5559,26 +5384,26 @@
         <v>13</v>
       </c>
       <c r="E96" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H96" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I96" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I96" s="2"/>
       <c r="J96" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>202</v>
       </c>
@@ -5589,20 +5414,18 @@
         <v>13</v>
       </c>
       <c r="E97" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>342</v>
+        <v>271</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H97" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>343</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I97" s="2"/>
       <c r="J97" s="3" t="s">
         <v>256</v>
       </c>
@@ -5610,7 +5433,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>204</v>
       </c>
@@ -5621,26 +5444,26 @@
         <v>13</v>
       </c>
       <c r="E98" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H98" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I98" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I98" s="2"/>
       <c r="J98" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>206</v>
       </c>
@@ -5651,26 +5474,26 @@
         <v>13</v>
       </c>
       <c r="E99" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H99" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I99" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I99" s="2"/>
       <c r="J99" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>208</v>
       </c>
@@ -5681,26 +5504,26 @@
         <v>13</v>
       </c>
       <c r="E100" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H100" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I100" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I100" s="2"/>
       <c r="J100" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>210</v>
       </c>
@@ -5711,26 +5534,26 @@
         <v>13</v>
       </c>
       <c r="E101" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H101" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I101" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I101" s="2"/>
       <c r="J101" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>212</v>
       </c>
@@ -5741,28 +5564,28 @@
         <v>13</v>
       </c>
       <c r="E102" t="s">
-        <v>355</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>344</v>
+        <v>273</v>
+      </c>
+      <c r="F102" t="s">
+        <v>212</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H102" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>214</v>
       </c>
@@ -5773,26 +5596,29 @@
         <v>13</v>
       </c>
       <c r="E103" t="s">
-        <v>355</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F103" t="s">
+        <v>214</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H103" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I103" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="J103" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M103" s="3"/>
+    </row>
+    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>216</v>
       </c>
@@ -5803,26 +5629,29 @@
         <v>13</v>
       </c>
       <c r="E104" t="s">
-        <v>355</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F104" t="s">
+        <v>216</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H104" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I104" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="J104" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M104" s="3"/>
+    </row>
+    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>218</v>
       </c>
@@ -5833,26 +5662,29 @@
         <v>13</v>
       </c>
       <c r="E105" t="s">
-        <v>355</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F105" t="s">
+        <v>218</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H105" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I105" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="J105" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M105" s="3"/>
+    </row>
+    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>220</v>
       </c>
@@ -5863,26 +5695,29 @@
         <v>13</v>
       </c>
       <c r="E106" t="s">
-        <v>355</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F106" t="s">
+        <v>220</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H106" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I106" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="J106" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M106" s="3"/>
+    </row>
+    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>222</v>
       </c>
@@ -5893,26 +5728,29 @@
         <v>13</v>
       </c>
       <c r="E107" t="s">
-        <v>355</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F107" t="s">
+        <v>222</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H107" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I107" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J107" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M107" s="3"/>
+    </row>
+    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>224</v>
       </c>
@@ -5923,26 +5761,26 @@
         <v>13</v>
       </c>
       <c r="E108" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H108" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I108" s="5"/>
       <c r="J108" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>226</v>
       </c>
@@ -5953,26 +5791,29 @@
         <v>13</v>
       </c>
       <c r="E109" t="s">
-        <v>355</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F109" t="s">
+        <v>226</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H109" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I109" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="J109" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M109" s="3"/>
+    </row>
+    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>228</v>
       </c>
@@ -5983,26 +5824,29 @@
         <v>13</v>
       </c>
       <c r="E110" t="s">
-        <v>355</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F110" t="s">
+        <v>228</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H110" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I110" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>332</v>
+      </c>
       <c r="J110" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M110" s="3"/>
+    </row>
+    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>230</v>
       </c>
@@ -6013,28 +5857,29 @@
         <v>13</v>
       </c>
       <c r="E111" t="s">
-        <v>355</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>346</v>
+        <v>273</v>
+      </c>
+      <c r="F111" t="s">
+        <v>230</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H111" s="15" t="s">
-        <v>394</v>
+        <v>253</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="M111" s="3"/>
+    </row>
+    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>232</v>
       </c>
@@ -6045,23 +5890,25 @@
         <v>13</v>
       </c>
       <c r="E112" t="s">
-        <v>355</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F112" t="s">
+        <v>232</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H112" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I112" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="J112" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
@@ -6075,23 +5922,25 @@
         <v>13</v>
       </c>
       <c r="E113" t="s">
-        <v>355</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F113" t="s">
+        <v>234</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H113" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I113" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>305</v>
+      </c>
       <c r="J113" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
@@ -6105,23 +5954,25 @@
         <v>13</v>
       </c>
       <c r="E114" t="s">
-        <v>355</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F114" t="s">
+        <v>236</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="I114" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="J114" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
@@ -6135,25 +5986,25 @@
         <v>13</v>
       </c>
       <c r="E115" t="s">
-        <v>355</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>349</v>
+        <v>273</v>
+      </c>
+      <c r="F115" t="s">
+        <v>238</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H115" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
@@ -6167,25 +6018,25 @@
         <v>13</v>
       </c>
       <c r="E116" t="s">
-        <v>355</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>396</v>
+        <v>273</v>
+      </c>
+      <c r="F116" t="s">
+        <v>240</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H116" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>395</v>
+        <v>277</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
@@ -6199,23 +6050,23 @@
         <v>13</v>
       </c>
       <c r="E117" t="s">
-        <v>355</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>348</v>
+        <v>273</v>
+      </c>
+      <c r="F117" t="s">
+        <v>242</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H117" s="15" t="s">
-        <v>348</v>
+        <v>253</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="I117" s="5"/>
       <c r="J117" s="3" t="s">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
@@ -6229,23 +6080,23 @@
         <v>13</v>
       </c>
       <c r="E118" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H118" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I118" s="5"/>
       <c r="J118" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
@@ -6259,23 +6110,23 @@
         <v>13</v>
       </c>
       <c r="E119" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H119" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I119" s="5"/>
       <c r="J119" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
@@ -6289,23 +6140,23 @@
         <v>13</v>
       </c>
       <c r="E120" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H120" s="15" t="s">
-        <v>348</v>
+        <v>271</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="I120" s="5"/>
       <c r="J120" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
@@ -6319,25 +6170,25 @@
         <v>252</v>
       </c>
       <c r="E121" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="F121" t="s">
-        <v>356</v>
+        <v>274</v>
       </c>
       <c r="G121" t="s">
-        <v>357</v>
-      </c>
-      <c r="H121" s="15">
+        <v>275</v>
+      </c>
+      <c r="H121" s="8">
         <v>2</v>
       </c>
       <c r="I121" t="s">
-        <v>397</v>
+        <v>278</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_IDEFICS_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_IDEFICS_FRANZI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{68140089-BBF9-486E-BCD1-79260BE80421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0315D801-E0A7-4EFC-A698-B29C5EB2EBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -849,9 +849,6 @@
     <t>IDEFICS_P1</t>
   </si>
   <si>
-    <t>_BLANK_</t>
-  </si>
-  <si>
     <t>paste</t>
   </si>
   <si>
@@ -1857,6 +1854,9 @@
       </rPr>
       <t xml:space="preserve"> SACANA FGS L47 "Based on potatoes")</t>
     </r>
+  </si>
+  <si>
+    <t>__BLANK__</t>
   </si>
 </sst>
 </file>
@@ -2362,7 +2362,7 @@
         <v>253</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>254</v>
@@ -2396,7 +2396,7 @@
         <v>253</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>254</v>
@@ -2461,7 +2461,7 @@
         <v>253</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>254</v>
@@ -2494,7 +2494,7 @@
         <v>253</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J6" s="16" t="s">
         <v>254</v>
@@ -2526,7 +2526,7 @@
         <v>253</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>254</v>
@@ -2558,7 +2558,7 @@
         <v>253</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>254</v>
@@ -2590,7 +2590,7 @@
         <v>253</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>254</v>
@@ -2622,7 +2622,7 @@
         <v>253</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>254</v>
@@ -2654,7 +2654,7 @@
         <v>253</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>254</v>
@@ -2686,7 +2686,7 @@
         <v>253</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>254</v>
@@ -2718,7 +2718,7 @@
         <v>253</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>254</v>
@@ -2750,7 +2750,7 @@
         <v>253</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>254</v>
@@ -2782,7 +2782,7 @@
         <v>253</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>254</v>
@@ -2844,7 +2844,7 @@
         <v>253</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>254</v>
@@ -2941,7 +2941,7 @@
         <v>253</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>254</v>
@@ -2974,7 +2974,7 @@
         <v>253</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>254</v>
@@ -3007,7 +3007,7 @@
         <v>253</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>254</v>
@@ -3136,7 +3136,7 @@
         <v>253</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J26" s="12" t="s">
         <v>254</v>
@@ -3169,7 +3169,7 @@
         <v>253</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J27" s="12" t="s">
         <v>254</v>
@@ -3201,7 +3201,7 @@
         <v>253</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>254</v>
@@ -3377,7 +3377,7 @@
         <v>253</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>254</v>
@@ -3440,7 +3440,7 @@
         <v>253</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>254</v>
@@ -3473,7 +3473,7 @@
         <v>253</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J36" s="12" t="s">
         <v>254</v>
@@ -3506,7 +3506,7 @@
         <v>253</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J37" s="12" t="s">
         <v>254</v>
@@ -3539,7 +3539,7 @@
         <v>253</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>254</v>
@@ -3572,7 +3572,7 @@
         <v>253</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J39" s="12" t="s">
         <v>254</v>
@@ -3605,7 +3605,7 @@
         <v>253</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>254</v>
@@ -3668,7 +3668,7 @@
         <v>253</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J42" s="15" t="s">
         <v>254</v>
@@ -3701,7 +3701,7 @@
         <v>253</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>254</v>
@@ -3734,7 +3734,7 @@
         <v>253</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>254</v>
@@ -3767,7 +3767,7 @@
         <v>253</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>254</v>
@@ -3800,7 +3800,7 @@
         <v>253</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>254</v>
@@ -3833,7 +3833,7 @@
         <v>253</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>254</v>
@@ -3927,7 +3927,7 @@
         <v>253</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>254</v>
@@ -3990,7 +3990,7 @@
         <v>253</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>254</v>
@@ -4023,7 +4023,7 @@
         <v>253</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>254</v>
@@ -4056,7 +4056,7 @@
         <v>253</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>254</v>
@@ -4182,7 +4182,7 @@
         <v>253</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>254</v>
@@ -4247,7 +4247,7 @@
         <v>253</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J60" s="12" t="s">
         <v>254</v>
@@ -4280,7 +4280,7 @@
         <v>253</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J61" s="7" t="s">
         <v>254</v>
@@ -4313,7 +4313,7 @@
         <v>253</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J62" s="7" t="s">
         <v>254</v>
@@ -4378,7 +4378,7 @@
         <v>253</v>
       </c>
       <c r="I64" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J64" s="15" t="s">
         <v>254</v>
@@ -4442,7 +4442,7 @@
         <v>253</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J66" s="7" t="s">
         <v>254</v>
@@ -4474,7 +4474,7 @@
         <v>253</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>254</v>
@@ -4506,7 +4506,7 @@
         <v>253</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J68" s="12" t="s">
         <v>254</v>
@@ -4662,7 +4662,7 @@
         <v>253</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>254</v>
@@ -4726,7 +4726,7 @@
         <v>253</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>254</v>
@@ -4758,7 +4758,7 @@
         <v>253</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>254</v>
@@ -4820,7 +4820,7 @@
         <v>253</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>254</v>
@@ -4853,10 +4853,10 @@
         <v>253</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K79" s="12" t="s">
         <v>255</v>
@@ -4886,10 +4886,10 @@
         <v>253</v>
       </c>
       <c r="I80" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K80" s="12" t="s">
         <v>255</v>
@@ -4919,10 +4919,10 @@
         <v>253</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K81" s="12" t="s">
         <v>255</v>
@@ -4952,7 +4952,7 @@
         <v>253</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>254</v>
@@ -5044,7 +5044,7 @@
         <v>253</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J85" s="7" t="s">
         <v>254</v>
@@ -5076,7 +5076,7 @@
         <v>253</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>254</v>
@@ -5108,7 +5108,7 @@
         <v>253</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>254</v>
@@ -5140,7 +5140,7 @@
         <v>253</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>254</v>
@@ -5173,7 +5173,7 @@
         <v>253</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>254</v>
@@ -5206,7 +5206,7 @@
         <v>253</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>254</v>
@@ -5239,7 +5239,7 @@
         <v>253</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>254</v>
@@ -5272,7 +5272,7 @@
         <v>253</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>254</v>
@@ -5576,7 +5576,7 @@
         <v>253</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>254</v>
@@ -5608,10 +5608,10 @@
         <v>253</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>255</v>
@@ -5641,7 +5641,7 @@
         <v>253</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>254</v>
@@ -5674,7 +5674,7 @@
         <v>253</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>254</v>
@@ -5707,7 +5707,7 @@
         <v>253</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>254</v>
@@ -5740,10 +5740,10 @@
         <v>253</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>255</v>
@@ -5803,10 +5803,10 @@
         <v>253</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>255</v>
@@ -5836,10 +5836,10 @@
         <v>253</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>255</v>
@@ -5869,7 +5869,7 @@
         <v>253</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J111" s="3" t="s">
         <v>254</v>
@@ -5902,10 +5902,10 @@
         <v>253</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>255</v>
@@ -5934,10 +5934,10 @@
         <v>253</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>255</v>
@@ -5966,10 +5966,10 @@
         <v>253</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>255</v>
@@ -6030,7 +6030,7 @@
         <v>253</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J116" s="3" t="s">
         <v>254</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="I117" s="5"/>
       <c r="J117" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K117" s="3" t="s">
         <v>255</v>
@@ -6173,16 +6173,16 @@
         <v>273</v>
       </c>
       <c r="F121" t="s">
+        <v>339</v>
+      </c>
+      <c r="G121" t="s">
         <v>274</v>
-      </c>
-      <c r="G121" t="s">
-        <v>275</v>
       </c>
       <c r="H121" s="8">
         <v>2</v>
       </c>
       <c r="I121" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J121" s="3" t="s">
         <v>254</v>
